--- a/artfynd/A 39773-2026 artfynd.xlsx
+++ b/artfynd/A 39773-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,60 +791,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99693830</v>
+        <v>137408704</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vändplan S Kolstugan, Srm</t>
+          <t>Kolstukärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587291</v>
+        <v>587071</v>
       </c>
       <c r="R3" t="n">
-        <v>6509470</v>
+        <v>6509336</v>
       </c>
       <c r="S3" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Andersson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Andersson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99693830</t>
+          <t>https://artportalen.se/Sighting/137408704</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99693834</v>
+        <v>137408903</v>
       </c>
       <c r="B4" t="n">
-        <v>58636</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,32 +932,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vändplan S Kolstugan, Srm</t>
+          <t>Kolstukärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587291</v>
+        <v>587106</v>
       </c>
       <c r="R4" t="n">
-        <v>6509470</v>
+        <v>6509368</v>
       </c>
       <c r="S4" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +970,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1000,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Andersson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Andersson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99693834</t>
+          <t>https://artportalen.se/Sighting/137408903</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744416</v>
+        <v>137410810</v>
       </c>
       <c r="B5" t="n">
-        <v>8460</v>
+        <v>57212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,37 +1028,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storö V, Srm</t>
+          <t>Kolstukärret, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587153</v>
+        <v>587066</v>
       </c>
       <c r="R5" t="n">
-        <v>6509358</v>
+        <v>6509291</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ex troligen ett par pickade grus på vägen när jag kom till platsen med bil.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,31 +1107,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122744416</t>
+          <t>https://artportalen.se/Sighting/137410810</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129968594</v>
+        <v>99693830</v>
       </c>
       <c r="B6" t="n">
-        <v>98050</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,46 +1135,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222112</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vändplan S Kolstugan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587302</v>
+        <v>587291</v>
       </c>
       <c r="R6" t="n">
-        <v>6509495</v>
+        <v>6509470</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,17 +1201,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 ex noterade på gräsbevuxen vändplan.</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,16 +1231,480 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Måreby</t>
+          <t>Mats Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Måreby</t>
+          <t>Mats Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99693830</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137408604</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kolstukärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587014</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6509304</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Karakteristiskt läte</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408604</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99693834</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vändplan S Kolstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587291</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6509470</v>
+      </c>
+      <c r="S8" t="n">
+        <v>58</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mats Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99693834</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122744416</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storö V, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>587153</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6509358</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744416</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129968594</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vändplan S Kolstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>587302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6509495</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 ex noterade på gräsbevuxen vändplan.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129968594</t>
         </is>
@@ -1266,6 +1717,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39773-2026 artfynd.xlsx
+++ b/artfynd/A 39773-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137408704</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137408903</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137410810</v>
       </c>
       <c r="B5" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137408604</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
